--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9941022</v>
+        <v>11071.58</v>
       </c>
     </row>
     <row r="3">
@@ -630,11 +630,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11780131.3</v>
+        <v>13119.85</v>
       </c>
     </row>
     <row r="4">
@@ -691,11 +691,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17004629.95</v>
+        <v>18938.51</v>
       </c>
     </row>
     <row r="5">
@@ -752,11 +752,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>11039217.75</v>
+        <v>12294.67</v>
       </c>
     </row>
     <row r="6">
@@ -813,11 +813,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>23833991.5</v>
+        <v>26544.56</v>
       </c>
     </row>
     <row r="7">
@@ -874,11 +874,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7960505</v>
+        <v>8865.83</v>
       </c>
     </row>
     <row r="8">
@@ -935,11 +935,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>21240514.12</v>
+        <v>23656.13</v>
       </c>
     </row>
     <row r="9">
@@ -996,11 +996,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10716614.7</v>
+        <v>11935.38</v>
       </c>
     </row>
     <row r="10">
@@ -1057,11 +1057,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10173607.5</v>
+        <v>11330.62</v>
       </c>
     </row>
     <row r="11">
@@ -1118,11 +1118,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>29456228.48</v>
+        <v>32806.19</v>
       </c>
     </row>
     <row r="12">
@@ -1179,11 +1179,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>58649994.9</v>
+        <v>65320.08</v>
       </c>
     </row>
     <row r="13">
@@ -1240,11 +1240,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>16639557.2</v>
+        <v>18531.92</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>31149313.35</v>
+        <v>34691.83</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6849122</v>
+        <v>7628.05</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>17873771.16</v>
+        <v>19906.5</v>
       </c>
     </row>
     <row r="17">
@@ -1484,11 +1484,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>27946227.75</v>
+        <v>31124.47</v>
       </c>
     </row>
     <row r="18">
@@ -1545,11 +1545,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5822715.08</v>
+        <v>6484.91</v>
       </c>
     </row>
     <row r="19">
@@ -1606,11 +1606,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>13406178.52</v>
+        <v>14930.82</v>
       </c>
     </row>
     <row r="20">
@@ -1667,11 +1667,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>17339983</v>
+        <v>19312.01</v>
       </c>
     </row>
     <row r="21">
@@ -1728,11 +1728,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6405141.85</v>
+        <v>7133.58</v>
       </c>
     </row>
     <row r="22">
@@ -1789,11 +1789,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6738923.94</v>
+        <v>7505.32</v>
       </c>
     </row>
     <row r="23">
@@ -1850,11 +1850,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>53636547.85</v>
+        <v>59736.47</v>
       </c>
     </row>
     <row r="24">
@@ -1911,11 +1911,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>24578399.02</v>
+        <v>27373.62</v>
       </c>
     </row>
     <row r="25">
@@ -1972,11 +1972,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7897792</v>
+        <v>8795.98</v>
       </c>
     </row>
     <row r="26">
@@ -2033,11 +2033,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>20501587.26</v>
+        <v>22833.17</v>
       </c>
     </row>
     <row r="27">
@@ -2094,11 +2094,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>58636341.35</v>
+        <v>65304.87</v>
       </c>
     </row>
     <row r="28">
@@ -2155,11 +2155,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>71532209.84999999</v>
+        <v>79667.35000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2216,11 +2216,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>26460202.5</v>
+        <v>29469.44</v>
       </c>
     </row>
     <row r="30">
@@ -2277,11 +2277,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7026384.75</v>
+        <v>7825.47</v>
       </c>
     </row>
     <row r="31">
@@ -2338,11 +2338,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>26667004.1</v>
+        <v>29699.76</v>
       </c>
     </row>
     <row r="32">
@@ -2399,11 +2399,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11730850</v>
+        <v>13064.96</v>
       </c>
     </row>
     <row r="33">
@@ -2460,11 +2460,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6849122</v>
+        <v>7628.05</v>
       </c>
     </row>
     <row r="34">
@@ -2521,11 +2521,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>50809668</v>
+        <v>56588.09</v>
       </c>
     </row>
     <row r="35">
@@ -2582,11 +2582,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>29802090.08</v>
+        <v>33191.39</v>
       </c>
     </row>
     <row r="36">
@@ -2643,11 +2643,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12785575</v>
+        <v>14239.64</v>
       </c>
     </row>
     <row r="37">
@@ -2704,11 +2704,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>28918501.5</v>
+        <v>32207.31</v>
       </c>
     </row>
     <row r="38">
@@ -2765,11 +2765,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>24909079.74</v>
+        <v>27741.91</v>
       </c>
     </row>
     <row r="39">
@@ -2826,11 +2826,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5830090.56</v>
+        <v>6493.13</v>
       </c>
     </row>
     <row r="40">
@@ -2887,11 +2887,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6859466.85</v>
+        <v>7639.57</v>
       </c>
     </row>
     <row r="41">
@@ -2948,11 +2948,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>12232509.8</v>
+        <v>13623.68</v>
       </c>
     </row>
     <row r="42">
@@ -3009,11 +3009,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7910877.52</v>
+        <v>8810.559999999999</v>
       </c>
     </row>
     <row r="43">
@@ -3070,11 +3070,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14762458.3</v>
+        <v>16441.35</v>
       </c>
     </row>
     <row r="44">
@@ -3135,11 +3135,11 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>62551229.02</v>
+        <v>69664.99000000001</v>
       </c>
     </row>
     <row r="45">
@@ -3196,11 +3196,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5821796.82</v>
+        <v>6483.89</v>
       </c>
     </row>
   </sheetData>
